--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_fea_004/extracted.xlsx
@@ -490,6 +490,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -680,6 +685,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -711,11 +721,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1368,17 +1373,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Collared Ti-6Al-4V Femoral Stem FEA — Design Freeze</t>
+          <t>Femoral Stem FEA — Design Freeze V&amp;V</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Cortical stress/strain and stem–bone micromotion prediction for immediate post-op single-leg stance to support design freeze</t>
+          <t>Predict cortical stress/strain and stem–bone micromotion under immediate post-op single-leg stance to support design freeze decision</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Nonlinear contact FEA (Abaqus/Standard 2023.HF2) is used to demonstrate that peak cortical von Mises stress and interface micromotion under immediate post-operative single-leg stance loading remain within acceptance limits. The model supports the design freeze decision for a collared Ti-6Al-4V femoral stem. It is not used for fatigue life, long-term remodeling, or osteoporotic populations. Valid for BMI 20–35, T-score &gt; −2.0, and normal immediate post-op conditions.</t>
+          <t>Nonlinear contact FEA (Abaqus/Standard 2023.HF2) of a collared Ti-6Al-4V femoral stem is used to demonstrate that cortical stress/strain and stem–bone interface micromotion under 2.2 kN single-leg stance loading remain within clinical safety targets for the immediate post-operative condition. The model supports a design freeze decision and is not used for long-term remodeling or fatigue life prediction. Valid for BMI 20–35, normal bone (T-score &gt; −2.0), and immediate post-op conditions.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1416,9 +1421,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2014,7 +2019,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Cortical stress and micromotion acceptance limits</t>
+          <t>Cortical Stress and Micromotion Safety Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2024,7 +2029,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Peak cortical von Mises stress must remain below 120 MPa and interface micromotion must remain below 50 μm (95th percentile under quantified uncertainty) to support design freeze without elevated periprosthetic fracture risk.</t>
+          <t>Peak cortical von Mises stress must remain below 120 MPa and interface micromotion must remain below 50 μm (95th percentile under uncertainty) to ensure acceptable periprosthetic fracture risk and osseointegration potential for immediate post-op single-leg stance</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2046,13 +2051,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Femoral Stem Contact FEA Model (MC-Stem-v1.6.x)</t>
+          <t>MD-StemFEA v1.6.2</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Small-strain nonlinear contact FEA in Abaqus/Standard 2023.HF2 with subject-specific heterogeneous bone moduli mapped from CT, frictional surface-to-surface contact, and ISO 7206-4-analog loading/boundary conditions.</t>
+          <t>Abaqus/Standard 2023.HF2 nonlinear contact FEA model of collared Ti-6Al-4V femoral stem with subject-specific heterogeneous bone moduli mapped from CT; frictional surface-to-surface contact; 1.8M C3D10 elements</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2066,13 +2071,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Cadaveric Femur Experimental Dataset (LD-ORS-2026-07)</t>
+          <t>LD-ORS-2026-07</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Strain gauge and DIC measurements from five cadaveric femurs tested under ISO 7206-4-analog fixture; provides ground-truth comparison data for model validation.</t>
+          <t>Cadaveric femur experimental dataset — 5 specimens, 12 strain gauges and DIC, ISO 7206-4 analog loading; used for validation of medial calcar principal strain and interface micromotion predictions</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2086,13 +2091,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>CT-to-Modulus Calibration Dataset</t>
+          <t>MC-Stem-v1.6.x / RL-2026-07-19 to RL-2026-08-01</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Subject-specific bone elastic moduli mapped from CT using a Keyak-type calibration (cortex 16–22 GPa, trabecular 0.1–1.5 GPa); used as model input and varied in uncertainty propagation.</t>
+          <t>Model configuration files and run logs for all simulation cases; all inputs and outputs unit-checked (SI) and archived with full provenance traceability</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2242,7 +2247,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Medial Calcar Principal Strain — Model vs. Cadaveric Bench Test</t>
+          <t>Strain Gauge and DIC Comparison — Cadaveric Femur Bench Test</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2257,12 +2262,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model-predicted medial calcar principal strain compared against strain gauge measurements from five cadaveric femur specimens under ISO 7206-4-analog loading. Friction coefficient tuned on two pilot specimens and locked prior to validation on the remaining five.</t>
+          <t>FEA-predicted medial calcar principal strain and interface micromotion compared against physical bench test data from 5 cadaveric femurs instrumented with 12 strain gauges and DIC, under loading conditions mirroring the simulation (ISO 7206-4 analog, same angles, potting, and fixture compliance)</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Cadaveric strain gauge measurements (±5 με) and DIC data (±3%) from dataset LD-ORS-2026-07</t>
+          <t>Experimental measurements from Lab dataset LD-ORS-2026-07</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2272,12 +2277,12 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t>Measurement uncertainty characterization (±5 με gauges, ±3% DIC); Latin hypercube sampling (500 samples) with first-order Sobol sensitivity indices</t>
+          <t>Measurement uncertainty quantified (±5 με gauges, ±3% DIC); alignment errors verified by photogrammetry (&lt;0.5°)</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>RMS error 7.4%, mean signed error +1.2%, R²=0.93 across all gauges; lateral cortex RMS 9.1%; interface micromotion MAPE 8.6%; no load-level bias (p=0.41)</t>
+          <t>Medial calcar RMS error 7.4%, mean signed error +1.2%; lateral cortex RMS 9.1%; R²=0.93 across all gauges; micromotion MAPE 8.6%; no load-level bias (p=0.41)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2289,7 +2294,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Mesh Convergence / Discretization Study</t>
+          <t>Mesh Convergence Study — GCI Analysis</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2300,12 +2305,12 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study at calcar and distal stem shoulder (0.8M, 1.8M, 4.2M C3D10 elements). Richardson extrapolation and GCI computed for peak von Mises stress. Primary QoIs monitored across mesh levels.</t>
+          <t>Mesh refinement study at calcar and distal stem shoulder using three mesh densities (0.8M, 1.8M, 4.2M C3D10 elements); Richardson extrapolation and GCI computed for peak von Mises stress; primary QoIs checked across finest two meshes</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated asymptotic value (~94 MPa)</t>
+          <t>Richardson extrapolation estimate (~94 MPa) and analytical asymptotic value</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
@@ -2320,7 +2325,7 @@
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>GCI ≈2.2% (apparent order p≈1.8); QoIs varied &lt;3% between two finest meshes</t>
+          <t>Peak von Mises 88.3/92.1/93.4 MPa across meshes; Richardson extrapolation ~94 MPa; fine-mesh GCI ~2.2% (p≈1.8); primary QoIs vary &lt;3% between two finest meshes</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2332,7 +2337,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Code Verification — Element and Contact Benchmark Tests</t>
+          <t>Uncertainty Propagation — Latin Hypercube Sampling</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2343,23 +2348,27 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Element-level patch test, three-point bending vs. Euler-Bernoulli beam theory, and Hertzian contact pressure distribution compared against analytic solutions to verify correct code implementation.</t>
+          <t>500-sample Latin hypercube study varying cortical modulus, trabecular modulus, friction coefficient, stem placement, load magnitude, and CT-to-modulus slope to characterize 95th percentile outputs and Sobol sensitivity indices</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Linear patch test analytic solution; Euler-Bernoulli beam theory; Hertzian contact analytic pressure distribution</t>
+          <t>Acceptance limits: peak cortical von Mises &lt;120 MPa; interface micromotion &lt;50 μm</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Latin hypercube sampling (500 samples); first-order Sobol sensitivity indices</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Patch test error &lt;0.5%; bending error &lt;1.0%; Hertzian contact within 3% of analytic</t>
+          <t>95th percentile peak cortical von Mises = 105 MPa (margin ~12% to 120 MPa limit); 95th percentile micromotion = 41 μm (&lt;50 μm target); dominant Sobol index: stem placement 0.41</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2371,7 +2380,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Uncertainty Propagation — 95th Percentile QoI Margins</t>
+          <t>Code Verification — Benchmark Problems</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2382,27 +2391,23 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Latin hypercube sampling (500 samples) propagating uncertainty in cortical/trabecular moduli, friction coefficient, stem placement, load magnitude, and CT-to-modulus slope through the FEA model. 95th percentile outputs compared to acceptance limits.</t>
+          <t>Element-level and benchmark verification tests: linear patch test, three-point bending vs Euler-Bernoulli analytical solution, and Hertzian contact pressure distribution vs analytical solution</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Acceptance limits: cortical von Mises ≤120 MPa; interface micromotion ≤50 μm</t>
+          <t>Analytical solutions (Euler-Bernoulli beam theory, Hertzian contact)</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling (500 samples); first-order Sobol sensitivity indices</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>95th-percentile peak cortical von Mises = 105 MPa (margin ≈12% to 120 MPa limit); 95th-percentile micromotion = 41 μm (margin ≈18% to 50 μm limit)</t>
+          <t>Patch test error &lt;0.5%; bending error &lt;1.0%; Hertzian contact error &lt;3%</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2636,12 +2641,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with documented QA; version control; CI testing; independent audit completed</t>
+          <t>Commercial solver with documented verification; version control; CI regression testing; independent audit</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023.HF2 is a commercial solver run in double precision on validated hardware. Models tracked in Git (repo MD-StemFEA, tag v1.6.2). Jenkins CI runs unit problems after each commit. Cross-platform reproducibility confirmed within 0.2%. Independent reviewer A. Nguyen (PhD, not on design team) completed a code/process audit on 23 Jul 2026 with no open actions. Evidence is thorough; an independent audit record is present.</t>
+          <t>Abaqus/Standard 2023.HF2 used in double precision. All models tracked in Git (repo MD-StemFEA, tag v1.6.2). Jenkins CI runs unit problems after each commit. Jobs reproduced on two platforms (CentOS 8 and Windows 11) within 0.2%. External independent reviewer A. Nguyen (PhD, not on design team) completed code/process audit on 23 Jul 2026 with no open actions.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2669,12 +2674,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Multiple benchmark comparisons to analytic solutions covering element behavior, structural response, and contact mechanics</t>
+          <t>Comparison to analytical solutions for representative physics including contact</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Three analytic benchmarks performed: (1) linear patch test error &lt;0.5%, (2) three-point bending vs. Euler-Bernoulli theory &lt;1.0% on coarse-to-fine meshes, (3) Hertzian contact pressure within 3% of analytic. These directly cover the dominant physics (structural elasticity, contact) in the model. Evidence is thorough with quantified errors against known solutions.</t>
+          <t>Element-level tests documented: linear patch test error &lt;0.5%, three-point bending vs Euler-Bernoulli &lt;1.0% across coarse-to-fine meshes, and Hertzian contact pressure distribution within 3% of analytic solution. These cover the primary physics (elasticity and contact) present in the stem model.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2702,12 +2707,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Formal mesh convergence study with GCI &lt;5% for primary QoIs; Richardson extrapolation performed</t>
+          <t>Mesh convergence study with GCI &lt;5% for primary QoIs</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three-level refinement study (0.8M/1.8M/4.2M C3D10 elements) at the critical calcar and distal stem shoulder regions. Richardson extrapolation yields asymptotic estimate ~94 MPa; fine-mesh GCI ≈2.2% (apparent order p≈1.8). Primary QoIs varied &lt;3% between the two finest meshes. Contact surfaces refined to overclosure &lt;1 μm. Evidence is thorough with quantified GCI.</t>
+          <t>Three-level mesh refinement study (0.8M/1.8M/4.2M C3D10 elements) performed at calcar and distal stem shoulder. Richardson extrapolation ~94 MPa; fine-mesh GCI ~2.2% (p≈1.8). Primary QoIs (medial principal strain, interface micromotion) varied &lt;3% across two finest meshes. Contact surfaces refined to limit overclosure &lt;1 μm.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2728,19 +2733,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Documented residual targets met; contact convergence confirmed; energy balance verified</t>
+          <t>Residual convergence targets met; contact stabilization documented</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Newton-Raphson residual &lt;1e-6 enforced; contact stabilization disabled; final contact penetration 0.3–0.9 μm; energy balance error &lt;0.6%. All convergence metrics are quantified and well within acceptable tolerances for nonlinear contact FEA.</t>
+          <t>Newton-Raphson residual tolerance &lt;1e-6; contact stabilization deliberately off; final contact penetration 0.3–0.9 μm; energy balance error &lt;0.6%. Convergence metrics fully documented and quantitatively reported.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2768,12 +2773,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary condition and load verification; unit checks</t>
+          <t>Independent review of model setup; boundary condition verification; mesh quality checks</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>External reviewer A. Nguyen (PhD, not on design team) completed a code/process audit on 23 Jul 2026 with no open actions. Loads and BCs explicitly mirror the physical test fixture (including fixture compliance 0.12 mm/kN). All inputs and outputs are unit-checked (SI) and linked to model configs MC-Stem-v1.6.x. Alignment errors &lt;0.5° verified by photogrammetry. Dataset and run-log traceability is fully documented.</t>
+          <t>External reviewer A. Nguyen (PhD, independent of design team) completed code/process audit on 23 Jul 2026 with no open actions. All inputs are unit-checked (SI). Boundary conditions (load angles, potting, fixture compliance 0.12 mm/kN) verified against rig configuration. Alignment verified by photogrammetry (&lt;0.5°). Full provenance tracked in Git and run logs.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2801,12 +2806,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations and contact formulation justified; model limitations explicitly documented</t>
+          <t>Governing equations justified for intended physics; known limitations explicitly documented</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Small-strain nonlinear contact FEA with frictional surface-to-surface contact is appropriate for the immediate post-op stance scenario. Known limitations are explicitly stated: no cyclic fatigue, no impaction damage, no osteolysis, valid only for BMI 20–35 and T-score &gt; −2.0. The Keyak-type CT-to-modulus calibration is a recognized approach. However, no formal turbulence/constitutive model validation paper is cited and the justification for model form choices (contact law, element type) is descriptive rather than referencing a dedicated model form validation study. Adequate but not fully documented with literature-cited constitutive validation.</t>
+          <t>Small-strain nonlinear contact FEA with frictional surface-to-surface contact is justified for immediate post-op quasi-static loading. Keyak-type CT-to-modulus calibration for heterogeneous bone is a well-established approach. Known limitations explicitly stated: no cyclic fatigue, no impaction damage, no osteolysis, no time-dependent behavior, no remodeling. Validity bounds stated (BMI 20–35, T-score &gt;−2.0, immediate post-op). Turbulence/constitutive model choice rationale is implicit rather than formally cited against alternative model forms, limiting level to 3.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2834,12 +2839,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from testing or established calibration; BCs from measurements; input uncertainty characterized and propagated</t>
+          <t>Material properties and boundary conditions from measurements or testing; input uncertainty characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Bone moduli from CT using Keyak-type calibration with uncertainty (CT-to-modulus slope ±10% in UQ). Friction coefficient tuned on two pilot specimens (μ=0.17) and locked. Load magnitudes, fixture compliance, and angular orientations taken from physical measurements. Stem placement uncertainty (±1 mm varus/valgus, ±1° rotation) and load magnitude uncertainty (±10%) all included in the 500-sample Latin hypercube. Input uncertainty is quantified and traceable to dataset LD-ORS-2026-07 and run logs.</t>
+          <t>Ti-6Al-4V properties specified (E=110 GPa, ν=0.34). Bone moduli mapped from CT with Keyak-type calibration (cortex 16–22 GPa, trabecular 0.1–1.5 GPa). Loads/BCs mirror physical fixture (2.2 kN at 20°, abductor 0.5 kN); fixture compliance measured (0.12 mm/kN) and included. Friction coefficient tuned on two pilot specimens (μ=0.17) then frozen before validation. Input uncertainty ranges defined for all major parameters and propagated via LHS (500 samples). Traceability via dataset LD-ORS-2026-07 and model configs MC-Stem-v1.6.x.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2860,19 +2865,19 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="41" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Adequate number of production-representative specimens; statistical characterization of specimen population</t>
+          <t>Adequate number of specimens representative of intended clinical population; statistical characterization</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Five cadaveric femurs used for validation (two additional pilots used only for friction tuning). The memo states test articles match CT density range and geometry within the intended cohort. However, n=5 is modest for statistical characterization; no formal power analysis or specimen population statistics (e.g., T-score distribution, BMI) are reported. Specimens are described as representative but not statistically characterized with confidence intervals on population coverage.</t>
+          <t>Five cadaveric femurs used for validation (two pilot specimens used only for friction tuning, then locked out). Test articles confirmed to match CT density range and geometry within the intended cohort. Sample size is modest (n=5) and lacks formal power analysis or statistical characterization of inter-specimen variability, which limits the level to 3.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2900,12 +2905,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation; controlled and measured loading conditions; measurement uncertainties reported; compliance with a recognized test standard</t>
+          <t>Calibrated instrumentation; controlled and measured test conditions; alignment verified; measurement uncertainty reported</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>ISO 7206-4-analog protocol applied. Twelve strain gauges (±5 με) and DIC (±3%) used. Fixture alignment verified by photogrammetry to &lt;0.5°. Fixture compliance measured at 0.12 mm/kN and incorporated into model. Loading angles and potting match model BCs. Measurement uncertainties are quantitatively reported for all primary instruments.</t>
+          <t>Instrumentation per ISO 7206-4 analog: 12 strain gauges (±5 με) and DIC (±3% calibrated). Alignment errors &lt;0.5° verified by photogrammetry. Fixture compliance measured (0.12 mm/kN). Same loading angles and potting as model. Measurement uncertainties quantitatively reported for all primary instruments.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2933,12 +2938,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Demonstrated one-to-one mapping of experimental conditions to model inputs; no free parameters after tuning</t>
+          <t>Model inputs demonstrably match experimental conditions; no unmatched free parameters</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>All loads/BCs in simulation explicitly duplicate the physical rig configuration. Fixture compliance included in model. Friction coefficient tuned on pilot specimens and then locked for all validation runs — no remaining free parameters. CT-to-modulus mapping applied consistently. Photogrammetry-verified alignment angles used as model input. Input-to-experiment correspondence is fully documented with dataset and run-log references.</t>
+          <t>All loads and BCs in the simulation duplicate the rig configuration explicitly. Fixture compliance included in model. Only one free parameter (friction coefficient μ) was tuned, using only the two pilot specimens, and then frozen before validation runs. No additional free parameters. Input parameter correspondence explicitly stated: "All inputs and outputs are unit-checked (SI) and linked."</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -2966,12 +2971,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative error metrics on primary QoIs; multiple comparison points; statistical validation metric; no significant bias</t>
+          <t>Quantitative error metrics; multiple comparison points; no systematic bias; R² or equivalent</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Medial calcar strain: RMS error 7.4%, mean signed error +1.2%, R²=0.93 across all gauges. Lateral cortex RMS 9.1%. Interface micromotion MAPE 8.6%. No load-level bias (p=0.41). Comparison spans 12 gauge locations plus DIC field data. All metrics fall within the stated 10% acceptance criterion. Uncertainty bands from UQ propagation are reported alongside acceptance limits. Evidence is thorough and quantitative.</t>
+          <t>Medial calcar principal strain: RMS error 7.4%, mean signed error +1.2%. Lateral cortex RMS 9.1%. R²=0.93 across all gauges. Interface micromotion MAPE 8.6% (DIC vs nodal relative slip). No bias with load level detected (p=0.41). Multiple comparison points across 12 gauge locations and DIC field. Overall within 10% target stated in memo.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -2999,12 +3004,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety/performance concern; measurable both computationally and experimentally</t>
+          <t>QoIs directly measure the safety/performance concern and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Primary QoIs — peak cortical von Mises stress/principal strain and interface micromotion — directly address the periprosthetic fracture risk and osseointegration concern identified in the hazard analysis. Both QoIs are measurable computationally (nodal outputs) and experimentally (strain gauges/DIC and DIC-derived relative slip). Acceptance limits (120 MPa, 50 μm) are linked to clinical safety targets. The decision-relevance is explicitly stated in the memo.</t>
+          <t>QoIs are medial calcar principal strain, lateral cortex strain, and stem–bone interface micromotion — directly linked to periprosthetic fracture risk and osseointegration (the stated clinical safety concerns). All QoIs are measurable experimentally (strain gauges, DIC) and computationally (nodal strain, nodal relative slip), enabling direct comparison. Acceptance limits (120 MPa, 50 μm) are tied to the decision criteria.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3032,12 +3037,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loading, population) match the full intended COU envelope; gaps documented</t>
+          <t>Validation conditions match COU operating conditions, geometry, loading, and population; gaps documented</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation cadaveric tests use the same loading configuration, fixture, and instrumentation as the model COU. Loading magnitudes and angles match immediate post-op single-leg stance. Geometry and density range match the intended cohort. Gaps are explicitly documented: no validation for fatigue, osteoporotic bone (T-score ≤ −2.0), BMI outside 20–35, impaction damage, or different CT-to-modulus calibrations. A planned two-specimen spot-check on production grit-blast surface finish is not yet complete. Coverage is adequate for the stated COU but the validation envelope does not span the full boundary of the applicability claims, and the production surface finish confirmation is outstanding.</t>
+          <t>Validation used cadaveric femurs with the same loading fixture, angles, and potting as the model, directly representing the immediate post-op single-leg stance COU. Geometry and CT density range confirmed to match intended cohort. Known gaps explicitly documented: no validation for fatigue, osteoporotic bone (T-score &lt; −2.0), BMI outside 20–35, long-term remodeling, or different CT-to-modulus calibrations. Guardrails documented in memo. A two-specimen spot-check on final production grit-blast surface finish remains open. These residual gaps limit the level to 3 despite good alignment within the stated scope.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3126,7 +3131,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The femoral stem FEA model meets the evidence bar established for the design freeze decision. Cortical strain RMS errors are within 10% (7.4% medial, 9.1% lateral), interface micromotion MAPE is 8.6%, and R²=0.93 across all gauge locations. Under quantified uncertainty (500-sample LHS, Sobol indices), 95th-percentile outputs preserve margins to both acceptance limits (105 MPa vs. 120 MPa; 41 μm vs. 50 μm). Mesh GCI is 2.2%, solver residuals and energy balance are well-controlled, and an independent audit confirmed no process deficiencies. Acceptance carries the following conditions recorded per the memo: (1) the model must not be reused for fatigue or osteoporotic cases without new validation data; (2) re-verification is required if collar/shoulder geometry changes exceed 1% or surface finish alters friction expectations beyond μ=0.17±0.03; (3) a two-specimen production grit-blast spot-check must be completed and archived before first-in-human use; (4) the full provenance package and reviewer sign-off must be archived in Windchill by 12 Aug 2026.</t>
+          <t>The femoral stem FEA package meets the evidence bar for the design freeze decision under the stated COU (immediate post-op, single-leg stance, BMI 20–35, T-score &gt;−2.0). Model-to-test agreement is within 10% on all primary QoIs (medial calcar RMS 7.4%, lateral cortex RMS 9.1%, micromotion MAPE 8.6%, R²=0.93). Under 500-sample LHS uncertainty propagation, 95th percentile peak cortical stress (105 MPa) and micromotion (41 μm) preserve margins to acceptance limits (120 MPa and 50 μm respectively). Mesh GCI ~2.2%, solver residuals &lt;1e-6, and energy balance error &lt;0.6% confirm numerical adequacy. Independent audit completed with no open actions. Acceptance is conditioned on: (1) not reusing the model for fatigue or osteoporotic cases without new data; (2) re-verification if geometry changes exceed 1% at collar/shoulder or surface finish alters friction expectations; (3) completion of two-specimen spot-check on final production grit-blast surface finish to confirm μ=0.17±0.03; and (4) archival of full provenance package and reviewer sign-off in Windchill by 12 Aug 2026.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
